--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260904.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>264,301,316</t>
+          <t>7,138,206</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>7,138,206</t>
+          <t>264,301,316</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>15,551,561</t>
+          <t>368,500,187</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>368,500,187</t>
+          <t>2,165,929</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,165,929</t>
+          <t>15,551,561</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>69,569,766</t>
+          <t>45,075,047</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>45,075,047</t>
+          <t>69,569,766</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
